--- a/data/stx_xlsx/ESSITYb.ST.xlsx
+++ b/data/stx_xlsx/ESSITYb.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="419">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -693,103 +693,109 @@
     <t>Loan receivables</t>
   </si>
   <si>
+    <t>Derivatives (Do not use)</t>
+  </si>
+  <si>
+    <t>Current financial assets - Balancing value</t>
+  </si>
+  <si>
+    <t>Non-current assets held for sale</t>
+  </si>
+  <si>
+    <t>Cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Current investments 3 months</t>
+  </si>
+  <si>
+    <t>Cash in Hand &amp; with Banks</t>
+  </si>
+  <si>
+    <t>Cash &amp; Cash Equivalents</t>
+  </si>
+  <si>
+    <t>Short-Term Investments</t>
+  </si>
+  <si>
+    <t>Total current assets</t>
+  </si>
+  <si>
+    <t>Assets held for sale</t>
+  </si>
+  <si>
+    <t>Total assets</t>
+  </si>
+  <si>
+    <t>Share capital</t>
+  </si>
+  <si>
+    <t>Reserves</t>
+  </si>
+  <si>
+    <t>Revaluation Reserves</t>
+  </si>
+  <si>
+    <t>Hedging Reserves</t>
+  </si>
+  <si>
+    <t>Translation Reserves</t>
+  </si>
+  <si>
+    <t>Retained earnings including profit/loss for the period</t>
+  </si>
+  <si>
+    <t>Equity attributable to owner of the Parent company</t>
+  </si>
+  <si>
+    <t>Minority Interest</t>
+  </si>
+  <si>
+    <t>Total equity</t>
+  </si>
+  <si>
+    <t>Non-current financial liabilities</t>
+  </si>
+  <si>
+    <t>Bonds (Do not use)</t>
+  </si>
+  <si>
+    <t>Non-current lease liabilities</t>
+  </si>
+  <si>
+    <t>Other Long-Term Loans with Maturity 1 year5 years</t>
+  </si>
+  <si>
+    <t>Other Long-Term Loans with Maturity 5 years</t>
+  </si>
+  <si>
+    <t>Non-current liabilities, Group companies</t>
+  </si>
+  <si>
+    <t>Provisions for pensions</t>
+  </si>
+  <si>
+    <t>Deferred tax liabilities</t>
+  </si>
+  <si>
+    <t>Other non-current provisions</t>
+  </si>
+  <si>
+    <t>Other non-current liabilities</t>
+  </si>
+  <si>
+    <t>Other Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>Total non-current liabilities</t>
+  </si>
+  <si>
+    <t>Current financial liabilities</t>
+  </si>
+  <si>
+    <t>Bonds</t>
+  </si>
+  <si>
     <t>Derivatives</t>
-  </si>
-  <si>
-    <t>Current financial assets - Balancing value</t>
-  </si>
-  <si>
-    <t>Non-current assets held for sale</t>
-  </si>
-  <si>
-    <t>Cash and cash equivalents</t>
-  </si>
-  <si>
-    <t>Current investments 3 months</t>
-  </si>
-  <si>
-    <t>Cash in Hand &amp; with Banks</t>
-  </si>
-  <si>
-    <t>Cash &amp; Cash Equivalents</t>
-  </si>
-  <si>
-    <t>Short-Term Investments</t>
-  </si>
-  <si>
-    <t>Total current assets</t>
-  </si>
-  <si>
-    <t>Assets held for sale</t>
-  </si>
-  <si>
-    <t>Total assets</t>
-  </si>
-  <si>
-    <t>Share capital</t>
-  </si>
-  <si>
-    <t>Reserves</t>
-  </si>
-  <si>
-    <t>Revaluation Reserves</t>
-  </si>
-  <si>
-    <t>Hedging Reserves</t>
-  </si>
-  <si>
-    <t>Translation Reserves</t>
-  </si>
-  <si>
-    <t>Retained earnings including profit/loss for the period</t>
-  </si>
-  <si>
-    <t>Equity attributable to owner of the Parent company</t>
-  </si>
-  <si>
-    <t>Minority Interest</t>
-  </si>
-  <si>
-    <t>Total equity</t>
-  </si>
-  <si>
-    <t>Non-current financial liabilities</t>
-  </si>
-  <si>
-    <t>Bonds</t>
-  </si>
-  <si>
-    <t>Non-current lease liabilities</t>
-  </si>
-  <si>
-    <t>Other Long-Term Loans with Maturity 1 year5 years</t>
-  </si>
-  <si>
-    <t>Other Long-Term Loans with Maturity 5 years</t>
-  </si>
-  <si>
-    <t>Non-current liabilities, Group companies</t>
-  </si>
-  <si>
-    <t>Provisions for pensions</t>
-  </si>
-  <si>
-    <t>Deferred tax liabilities</t>
-  </si>
-  <si>
-    <t>Other non-current provisions</t>
-  </si>
-  <si>
-    <t>Other non-current liabilities</t>
-  </si>
-  <si>
-    <t>Other Non-Current Liabilities</t>
-  </si>
-  <si>
-    <t>Total non-current liabilities</t>
-  </si>
-  <si>
-    <t>Current financial liabilities</t>
   </si>
   <si>
     <t>Current Portion of Long-Term Debt excluding Capitalized Leases</t>
@@ -1395,7 +1401,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1476,6 +1482,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -9570,7 +9579,7 @@
       <c r="M77" s="15"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="27" t="s">
         <v>224</v>
       </c>
       <c r="B78" s="18">
@@ -10333,7 +10342,7 @@
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="1">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="27" t="s">
         <v>245</v>
       </c>
       <c r="B101" s="15">
@@ -10374,7 +10383,7 @@
       </c>
     </row>
     <row r="102" ht="15.0" customHeight="1">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="27" t="s">
         <v>224</v>
       </c>
       <c r="B102" s="18">
@@ -10742,7 +10751,7 @@
       <c r="M111" s="15"/>
     </row>
     <row r="112" ht="15.0" customHeight="1">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="27" t="s">
         <v>224</v>
       </c>
       <c r="B112" s="19">
@@ -10848,7 +10857,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B115" s="18">
         <v>5951.74</v>
@@ -10889,7 +10898,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="B116" s="18">
         <v>482.22</v>
@@ -10930,7 +10939,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B117" s="18">
         <v>289.77</v>
@@ -10976,7 +10985,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B118" s="18">
         <v>1066.13</v>
@@ -10999,25 +11008,25 @@
       <c r="H118" s="18">
         <v>797.95</v>
       </c>
-      <c r="I118" s="27">
+      <c r="I118" s="28">
         <v>750.0</v>
       </c>
-      <c r="J118" s="27">
+      <c r="J118" s="28">
         <v>750.0</v>
       </c>
-      <c r="K118" s="27">
+      <c r="K118" s="28">
         <v>750.0</v>
       </c>
-      <c r="L118" s="27">
+      <c r="L118" s="28">
         <v>750.0</v>
       </c>
-      <c r="M118" s="27">
+      <c r="M118" s="28">
         <v>750.0</v>
       </c>
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -11044,7 +11053,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B120" s="18">
         <v>133.4</v>
@@ -11085,7 +11094,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -11112,7 +11121,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -11139,7 +11148,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -11166,7 +11175,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B124" s="15">
         <v>15786.38</v>
@@ -11207,7 +11216,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B125" s="18">
         <v>2019.63</v>
@@ -11248,7 +11257,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B126" s="18">
         <v>1312.16</v>
@@ -11289,7 +11298,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B127" s="15">
         <v>17567.64</v>
@@ -11330,7 +11339,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B128" s="18">
         <v>408.96</v>
@@ -11371,7 +11380,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B129" s="15">
         <v>13985.44</v>
@@ -11412,7 +11421,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B130" s="18">
         <v>3173.24</v>
@@ -11453,7 +11462,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B131" s="17">
         <v>44609.07</v>
@@ -11494,7 +11503,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="15">
@@ -11515,7 +11524,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="16" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B133" s="17">
         <v>88653.9</v>
@@ -11556,7 +11565,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="16" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B134" s="17">
         <v>182735.78</v>
@@ -11597,7 +11606,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B135" s="18">
         <v>683.05</v>
@@ -11638,7 +11647,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B136" s="19">
         <v>10.01</v>
@@ -11679,7 +11688,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B137" s="18">
         <v>693.05</v>
@@ -11720,7 +11729,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B138" s="18">
         <v>1213.75</v>
@@ -11751,7 +11760,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B139" s="18">
         <v>1645.67</v>
@@ -11782,7 +11791,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B140" s="18">
         <v>911.95</v>
@@ -11813,7 +11822,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B141" s="18">
         <v>1110.96</v>
@@ -11844,7 +11853,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -11869,7 +11878,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B143" s="18">
         <v>6570.64</v>
@@ -11900,7 +11909,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B144" s="18">
         <v>5957.21</v>
@@ -11931,7 +11940,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B145" s="15">
         <v>14782.58</v>
@@ -11962,7 +11971,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B146" s="15">
         <v>10574.92</v>
@@ -11993,7 +12002,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -12018,7 +12027,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B148" s="15">
         <v>14427.2</v>
@@ -12039,7 +12048,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B149" s="19">
         <v>58.2</v>
@@ -12080,7 +12089,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -12115,7 +12124,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B151" s="19">
         <v>58.2</v>
@@ -12156,7 +12165,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B152" s="19">
         <v>0.09</v>
@@ -12197,7 +12206,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B153" s="18">
         <v>634.85</v>
@@ -12238,7 +12247,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B154" s="19">
         <v>10.01</v>
@@ -12279,7 +12288,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B155" s="18">
         <v>624.85</v>
@@ -12320,7 +12329,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B156" s="19">
         <v>0.91</v>
@@ -12361,7 +12370,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -12386,7 +12395,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -12413,7 +12422,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -12440,7 +12449,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -12467,7 +12476,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -12494,7 +12503,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B162" s="15">
         <v>109579.0</v>
@@ -13389,7 +13398,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13645,40 +13654,40 @@
         <v>34</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -13724,7 +13733,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -13782,7 +13791,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B20" s="19">
         <v>4.24</v>
@@ -13801,7 +13810,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -13822,7 +13831,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -13841,7 +13850,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B23" s="18">
         <v>479.8</v>
@@ -13866,7 +13875,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B24" s="20">
         <v>-518.99</v>
@@ -13889,7 +13898,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -13908,7 +13917,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15">
@@ -13986,7 +13995,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B28" s="18">
         <v>8237.11</v>
@@ -14027,7 +14036,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B29" s="18">
         <v>7580.43</v>
@@ -14068,7 +14077,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B30" s="21">
         <v>-36.01</v>
@@ -14109,7 +14118,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -14136,7 +14145,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15">
@@ -14175,7 +14184,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B33" s="18">
         <v>112.27</v>
@@ -14210,7 +14219,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -14229,7 +14238,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -14250,7 +14259,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -14269,7 +14278,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -14294,7 +14303,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B38" s="19">
         <v>96.38</v>
@@ -14329,7 +14338,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -14352,7 +14361,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B40" s="20">
         <v>-4991.83</v>
@@ -14393,7 +14402,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B41" s="20">
         <v>-2821.61</v>
@@ -14428,7 +14437,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B42" s="18">
         <v>292.33</v>
@@ -14463,7 +14472,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -14482,7 +14491,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B44" s="21">
         <v>-86.85</v>
@@ -14515,7 +14524,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B45" s="20">
         <v>-244.67</v>
@@ -14550,7 +14559,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B46" s="20">
         <v>-970.19</v>
@@ -14591,7 +14600,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B47" s="18">
         <v>903.47</v>
@@ -14632,7 +14641,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B48" s="15">
         <v>0.0</v>
@@ -14655,7 +14664,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B49" s="20">
         <v>-3052.51</v>
@@ -14696,7 +14705,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B50" s="17">
         <v>16373.6</v>
@@ -14737,7 +14746,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B51" s="15">
         <v>0.0</v>
@@ -14778,7 +14787,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B52" s="19">
         <v>5.3</v>
@@ -14819,7 +14828,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B53" s="20">
         <v>-7509.46</v>
@@ -14860,7 +14869,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B54" s="18">
         <v>217.13</v>
@@ -14901,7 +14910,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="20">
@@ -14940,7 +14949,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B56" s="18">
         <v>3889.25</v>
@@ -14959,7 +14968,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -14990,7 +14999,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B58" s="15">
         <v>0.0</v>
@@ -15013,7 +15022,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B59" s="21">
         <v>-13.77</v>
@@ -15046,7 +15055,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -15069,7 +15078,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B61" s="23">
         <v>-3411.56</v>
@@ -15080,10 +15089,10 @@
       <c r="D61" s="23">
         <v>-7075.42</v>
       </c>
-      <c r="E61" s="28">
+      <c r="E61" s="29">
         <v>-13777.1</v>
       </c>
-      <c r="F61" s="28">
+      <c r="F61" s="29">
         <v>-12159.78</v>
       </c>
       <c r="G61" s="23">
@@ -15095,7 +15104,7 @@
       <c r="I61" s="23">
         <v>-6543.1</v>
       </c>
-      <c r="J61" s="28">
+      <c r="J61" s="29">
         <v>-18661.0</v>
       </c>
       <c r="K61" s="23">
@@ -15110,7 +15119,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -15145,7 +15154,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B63" s="15">
         <v>0.0</v>
@@ -15182,7 +15191,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B64" s="20">
         <v>-6048.88</v>
@@ -15217,7 +15226,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -15242,7 +15251,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B66" s="18">
         <v>1058.1</v>
@@ -15281,7 +15290,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B67" s="20">
         <v>-5479.05</v>
@@ -15320,7 +15329,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B68" s="20">
         <v>-1154.49</v>
@@ -15341,7 +15350,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="19">
@@ -15360,7 +15369,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B70" s="20">
         <v>-264.79</v>
@@ -15379,7 +15388,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -15398,7 +15407,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -15417,7 +15426,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B73" s="21">
         <v>-21.18</v>
@@ -15458,7 +15467,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B74" s="20">
         <v>-3346.95</v>
@@ -15479,7 +15488,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B75" s="15">
         <v>0.0</v>
@@ -15502,7 +15511,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -15529,15 +15538,15 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="B77" s="28">
+        <v>357</v>
+      </c>
+      <c r="B77" s="29">
         <v>-15257.24</v>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="29">
         <v>-22715.66</v>
       </c>
-      <c r="D77" s="28">
+      <c r="D77" s="29">
         <v>-11496.44</v>
       </c>
       <c r="E77" s="22">
@@ -15549,7 +15558,7 @@
       <c r="G77" s="23">
         <v>-8571.66</v>
       </c>
-      <c r="H77" s="28">
+      <c r="H77" s="29">
         <v>-12683.86</v>
       </c>
       <c r="I77" s="23">
@@ -15570,7 +15579,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B78" s="15">
         <v>11986.58</v>
@@ -15611,7 +15620,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B79" s="18">
         <v>9280.25</v>
@@ -15652,7 +15661,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B80" s="20">
         <v>-2295.21</v>
@@ -15693,7 +15702,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B81" s="20">
         <v>-326.22</v>
@@ -15734,7 +15743,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B82" s="23">
         <v>-2621.43</v>
@@ -15754,7 +15763,7 @@
       <c r="G82" s="22">
         <v>2102.23</v>
       </c>
-      <c r="H82" s="29">
+      <c r="H82" s="30">
         <v>-74.45</v>
       </c>
       <c r="I82" s="23">
@@ -15775,7 +15784,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -15802,7 +15811,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -15825,7 +15834,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -16783,7 +16792,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17118,7 +17127,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -17175,1397 +17184,1397 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
+      <c r="A20" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="B21" s="33">
+      <c r="A21" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" s="34">
         <v>232098.7</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>242984.93</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <v>236330.11</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>247727.38</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>262032.08</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>245649.26</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <v>251666.64</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <v>205494.89</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <v>219628.25</v>
       </c>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="B22" s="33">
+      <c r="A22" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="B22" s="34">
         <v>265817.75</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="34">
         <v>254653.77</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <v>255824.2</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <v>234631.52</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <v>234345.85</v>
       </c>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
+      <c r="A23" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="32" t="s">
-        <v>368</v>
-      </c>
-      <c r="B24" s="33">
+      <c r="A24" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="B24" s="34">
         <v>200996.14</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="34">
         <v>213505.32</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <v>176681.32</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <v>180601.05</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <v>202171.42</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <v>194367.52</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <v>198735.57</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <v>149165.34</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="34">
         <v>163668.11</v>
       </c>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="B25" s="33">
+      <c r="A25" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B25" s="34">
         <v>211336.43</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <v>199179.99</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="34">
         <v>195908.61</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <v>178901.09</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <v>179659.79</v>
       </c>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
+      <c r="A26" s="31" t="s">
+        <v>372</v>
+      </c>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="B27" s="34">
+      <c r="A27" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="B27" s="35">
         <v>289.99</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>304.01</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>251.69</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>256.02</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <v>288.39</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <v>276.19</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <v>282.99</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="35">
         <v>212.35</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="35">
         <v>233.15</v>
       </c>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="B28" s="34">
+      <c r="A28" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="B28" s="35">
         <v>301.71</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>283.53</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="35">
         <v>278.87</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="35">
         <v>255.65</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="35">
         <v>256.76</v>
       </c>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
+      <c r="A29" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="32" t="s">
-        <v>374</v>
-      </c>
-      <c r="B30" s="35">
+      <c r="A30" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="B30" s="36">
         <v>4.57</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="36">
         <v>4.7</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>6.94</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>3.1</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>3.52</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>6.04</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>6.32</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>4.09</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <v>4.01</v>
       </c>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="B31" s="35">
+      <c r="A31" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="B31" s="36">
         <v>4.51</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>4.79</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="36">
         <v>5.14</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>4.62</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="36">
         <v>4.84</v>
       </c>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
+      <c r="A32" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="B33" s="36">
         <v>2.18</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>1.83</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>2.03</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>1.79</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>1.6</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>1.65</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>1.33</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>1.85</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>0.0</v>
       </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="B34" s="36">
         <v>1.88</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>1.78</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>1.67</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>1.63</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>1.31</v>
       </c>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="32" t="s">
-        <v>379</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="B35" s="36">
         <v>3.11</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>2.62</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>2.9</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>2.56</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>2.29</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>2.36</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>1.91</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>2.64</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>0.0</v>
       </c>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="35"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" s="36">
         <v>2.68</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>2.54</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>2.38</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>2.33</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>1.87</v>
       </c>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
+      <c r="A37" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="B38" s="36">
+      <c r="A38" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="B38" s="37">
         <v>2.12</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="37">
         <v>2.33</v>
       </c>
-      <c r="D38" s="36">
+      <c r="D38" s="37">
         <v>2.48</v>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="37">
         <v>2.85</v>
       </c>
-      <c r="F38" s="36">
+      <c r="F38" s="37">
         <v>3.47</v>
       </c>
-      <c r="G38" s="36">
+      <c r="G38" s="37">
         <v>3.42</v>
       </c>
-      <c r="H38" s="36">
+      <c r="H38" s="37">
         <v>3.92</v>
       </c>
-      <c r="I38" s="36">
+      <c r="I38" s="37">
         <v>3.24</v>
       </c>
-      <c r="J38" s="36">
+      <c r="J38" s="37">
         <v>3.87</v>
       </c>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="34"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="32" t="s">
-        <v>383</v>
-      </c>
-      <c r="B39" s="36">
+      <c r="A39" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="B39" s="37">
         <v>2.58</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="37">
         <v>2.83</v>
       </c>
-      <c r="D39" s="36">
+      <c r="D39" s="37">
         <v>3.17</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="37">
         <v>3.36</v>
       </c>
-      <c r="F39" s="36">
+      <c r="F39" s="37">
         <v>3.58</v>
       </c>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
+      <c r="A40" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="B41" s="36">
+      <c r="A41" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" s="37">
         <v>5.94</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="37">
         <v>7.77</v>
       </c>
-      <c r="D41" s="36">
+      <c r="D41" s="37">
         <v>17.28</v>
       </c>
-      <c r="E41" s="33"/>
-      <c r="F41" s="34">
+      <c r="E41" s="34"/>
+      <c r="F41" s="35">
         <v>784.5</v>
       </c>
-      <c r="G41" s="36">
+      <c r="G41" s="37">
         <v>53.78</v>
       </c>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="34"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="B42" s="36">
+      <c r="A42" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="B42" s="37">
         <v>14.74</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="37">
         <v>25.61</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="35">
         <v>102.84</v>
       </c>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
+      <c r="A43" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="32" t="s">
-        <v>388</v>
-      </c>
-      <c r="B44" s="36">
+      <c r="A44" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="B44" s="37">
         <v>1.32</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="37">
         <v>1.42</v>
       </c>
-      <c r="D44" s="36">
+      <c r="D44" s="37">
         <v>1.19</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="37">
         <v>1.46</v>
       </c>
-      <c r="F44" s="36">
+      <c r="F44" s="37">
         <v>2.04</v>
       </c>
-      <c r="G44" s="36">
+      <c r="G44" s="37">
         <v>1.53</v>
       </c>
-      <c r="H44" s="36">
+      <c r="H44" s="37">
         <v>1.64</v>
       </c>
-      <c r="I44" s="36">
+      <c r="I44" s="37">
         <v>1.29</v>
       </c>
-      <c r="J44" s="36">
+      <c r="J44" s="37">
         <v>1.5</v>
       </c>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="34"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="32" t="s">
-        <v>389</v>
-      </c>
-      <c r="B45" s="36">
+      <c r="A45" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="B45" s="37">
         <v>1.45</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="37">
         <v>1.5</v>
       </c>
-      <c r="D45" s="36">
+      <c r="D45" s="37">
         <v>1.54</v>
       </c>
-      <c r="E45" s="36">
+      <c r="E45" s="37">
         <v>1.58</v>
       </c>
-      <c r="F45" s="36">
+      <c r="F45" s="37">
         <v>1.59</v>
       </c>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="33"/>
-      <c r="M45" s="33"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="34"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
+      <c r="A46" s="31" t="s">
+        <v>392</v>
+      </c>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="32" t="s">
-        <v>391</v>
-      </c>
-      <c r="B47" s="36">
+      <c r="A47" s="33" t="s">
+        <v>393</v>
+      </c>
+      <c r="B47" s="37">
         <v>21.87</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="37">
         <v>21.27</v>
       </c>
-      <c r="D47" s="36">
+      <c r="D47" s="37">
         <v>14.41</v>
       </c>
-      <c r="E47" s="36">
+      <c r="E47" s="37">
         <v>32.24</v>
       </c>
-      <c r="F47" s="36">
+      <c r="F47" s="37">
         <v>28.44</v>
       </c>
-      <c r="G47" s="36">
+      <c r="G47" s="37">
         <v>16.57</v>
       </c>
-      <c r="H47" s="36">
+      <c r="H47" s="37">
         <v>15.81</v>
       </c>
-      <c r="I47" s="36">
+      <c r="I47" s="37">
         <v>24.44</v>
       </c>
-      <c r="J47" s="36">
+      <c r="J47" s="37">
         <v>24.91</v>
       </c>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>392</v>
-      </c>
-      <c r="B48" s="36">
+      <c r="A48" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="B48" s="37">
         <v>22.17</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="37">
         <v>20.87</v>
       </c>
-      <c r="D48" s="36">
+      <c r="D48" s="37">
         <v>19.44</v>
       </c>
-      <c r="E48" s="36">
+      <c r="E48" s="37">
         <v>21.62</v>
       </c>
-      <c r="F48" s="36">
+      <c r="F48" s="37">
         <v>20.68</v>
       </c>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="34"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
+      <c r="A49" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="B50" s="36">
+      <c r="A50" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="B50" s="37">
         <v>9.23</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="37">
         <v>10.75</v>
       </c>
-      <c r="D50" s="36">
+      <c r="D50" s="37">
         <v>10.52</v>
       </c>
-      <c r="E50" s="36">
+      <c r="E50" s="37">
         <v>14.82</v>
       </c>
-      <c r="F50" s="36">
+      <c r="F50" s="37">
         <v>13.93</v>
       </c>
-      <c r="G50" s="36">
+      <c r="G50" s="37">
         <v>9.73</v>
       </c>
-      <c r="H50" s="36">
+      <c r="H50" s="37">
         <v>11.98</v>
       </c>
-      <c r="I50" s="36">
+      <c r="I50" s="37">
         <v>10.38</v>
       </c>
-      <c r="J50" s="36">
+      <c r="J50" s="37">
         <v>11.28</v>
       </c>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="33"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="34"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="32" t="s">
-        <v>395</v>
-      </c>
-      <c r="B51" s="36">
+      <c r="A51" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="B51" s="37">
         <v>11.53</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="37">
         <v>11.68</v>
       </c>
-      <c r="D51" s="36">
+      <c r="D51" s="37">
         <v>11.96</v>
       </c>
-      <c r="E51" s="36">
+      <c r="E51" s="37">
         <v>11.97</v>
       </c>
-      <c r="F51" s="36">
+      <c r="F51" s="37">
         <v>11.39</v>
       </c>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="33"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="34"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>396</v>
-      </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
+      <c r="A52" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="32" t="s">
-        <v>397</v>
-      </c>
-      <c r="B53" s="36">
+      <c r="A53" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="B53" s="37">
         <v>14.44</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="37">
         <v>17.3</v>
       </c>
-      <c r="D53" s="36">
+      <c r="D53" s="37">
         <v>18.6</v>
       </c>
-      <c r="E53" s="36">
+      <c r="E53" s="37">
         <v>37.56</v>
       </c>
-      <c r="F53" s="36">
+      <c r="F53" s="37">
         <v>26.96</v>
       </c>
-      <c r="G53" s="36">
+      <c r="G53" s="37">
         <v>18.16</v>
       </c>
-      <c r="H53" s="36">
+      <c r="H53" s="37">
         <v>23.0</v>
       </c>
-      <c r="I53" s="36">
+      <c r="I53" s="37">
         <v>19.38</v>
       </c>
-      <c r="J53" s="36">
+      <c r="J53" s="37">
         <v>20.16</v>
       </c>
-      <c r="K53" s="33"/>
-      <c r="L53" s="33"/>
-      <c r="M53" s="33"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="34"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="32" t="s">
-        <v>398</v>
-      </c>
-      <c r="B54" s="36">
+      <c r="A54" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="B54" s="37">
         <v>20.55</v>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="37">
         <v>21.77</v>
       </c>
-      <c r="D54" s="36">
+      <c r="D54" s="37">
         <v>23.33</v>
       </c>
-      <c r="E54" s="36">
+      <c r="E54" s="37">
         <v>23.67</v>
       </c>
-      <c r="F54" s="36">
+      <c r="F54" s="37">
         <v>21.36</v>
       </c>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
+      <c r="A55" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="32" t="s">
-        <v>400</v>
-      </c>
-      <c r="B56" s="36">
+      <c r="A56" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="B56" s="37">
         <v>13.49</v>
       </c>
-      <c r="C56" s="36">
+      <c r="C56" s="37">
         <v>14.59</v>
       </c>
-      <c r="D56" s="36">
+      <c r="D56" s="37">
         <v>14.45</v>
       </c>
-      <c r="E56" s="36">
+      <c r="E56" s="37">
         <v>25.43</v>
       </c>
-      <c r="F56" s="36">
+      <c r="F56" s="37">
         <v>28.25</v>
       </c>
-      <c r="G56" s="36">
+      <c r="G56" s="37">
         <v>17.3</v>
       </c>
-      <c r="H56" s="36">
+      <c r="H56" s="37">
         <v>22.64</v>
       </c>
-      <c r="I56" s="36">
+      <c r="I56" s="37">
         <v>15.48</v>
       </c>
-      <c r="J56" s="36">
+      <c r="J56" s="37">
         <v>17.39</v>
       </c>
-      <c r="K56" s="33"/>
-      <c r="L56" s="33"/>
-      <c r="M56" s="33"/>
+      <c r="K56" s="34"/>
+      <c r="L56" s="34"/>
+      <c r="M56" s="34"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="32" t="s">
-        <v>401</v>
-      </c>
-      <c r="B57" s="36">
+      <c r="A57" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="B57" s="37">
         <v>2.58</v>
       </c>
-      <c r="C57" s="36">
+      <c r="C57" s="37">
         <v>2.83</v>
       </c>
-      <c r="D57" s="36">
+      <c r="D57" s="37">
         <v>3.17</v>
       </c>
-      <c r="E57" s="36">
+      <c r="E57" s="37">
         <v>3.37</v>
       </c>
-      <c r="F57" s="36">
+      <c r="F57" s="37">
         <v>3.59</v>
       </c>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="33"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="33"/>
-      <c r="L57" s="33"/>
-      <c r="M57" s="33"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="34"/>
+      <c r="M57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
+      <c r="A58" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="32" t="s">
-        <v>403</v>
-      </c>
-      <c r="B59" s="36">
+      <c r="A59" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="B59" s="37">
         <v>1.93</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="37">
         <v>0.64</v>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="37">
         <v>0.22</v>
       </c>
-      <c r="E59" s="37">
+      <c r="E59" s="38">
         <v>-1.12</v>
       </c>
-      <c r="F59" s="37">
+      <c r="F59" s="38">
         <v>-1.09</v>
       </c>
-      <c r="G59" s="36">
+      <c r="G59" s="37">
         <v>1.65</v>
       </c>
-      <c r="H59" s="36">
+      <c r="H59" s="37">
         <v>1.36</v>
       </c>
-      <c r="I59" s="37">
+      <c r="I59" s="38">
         <v>-6.84</v>
       </c>
-      <c r="J59" s="36">
+      <c r="J59" s="37">
         <v>0.18</v>
       </c>
-      <c r="K59" s="33"/>
-      <c r="L59" s="33"/>
-      <c r="M59" s="33"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="34"/>
+      <c r="M59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="32" t="s">
-        <v>404</v>
-      </c>
-      <c r="B60" s="36">
+      <c r="A60" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="B60" s="37">
         <v>4.32</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="37">
         <v>4.01</v>
       </c>
-      <c r="D60" s="36">
+      <c r="D60" s="37">
         <v>6.37</v>
       </c>
-      <c r="E60" s="37">
+      <c r="E60" s="38">
         <v>-2.68</v>
       </c>
-      <c r="F60" s="36">
+      <c r="F60" s="37">
         <v>1.41</v>
       </c>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
-      <c r="M60" s="33"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
+      <c r="A61" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="32" t="s">
-        <v>406</v>
-      </c>
-      <c r="B62" s="36">
+      <c r="A62" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="B62" s="37">
         <v>1.53</v>
       </c>
-      <c r="C62" s="36">
+      <c r="C62" s="37">
         <v>1.62</v>
       </c>
-      <c r="D62" s="36">
+      <c r="D62" s="37">
         <v>1.6</v>
       </c>
-      <c r="E62" s="36">
+      <c r="E62" s="37">
         <v>2.0</v>
       </c>
-      <c r="F62" s="36">
+      <c r="F62" s="37">
         <v>2.65</v>
       </c>
-      <c r="G62" s="36">
+      <c r="G62" s="37">
         <v>1.93</v>
       </c>
-      <c r="H62" s="36">
+      <c r="H62" s="37">
         <v>2.08</v>
       </c>
-      <c r="I62" s="36">
+      <c r="I62" s="37">
         <v>1.78</v>
       </c>
-      <c r="J62" s="36">
+      <c r="J62" s="37">
         <v>2.01</v>
       </c>
-      <c r="K62" s="33"/>
-      <c r="L62" s="33"/>
-      <c r="M62" s="33"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="34"/>
+      <c r="M62" s="34"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="32" t="s">
-        <v>407</v>
-      </c>
-      <c r="B63" s="36">
+      <c r="A63" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="B63" s="37">
         <v>1.83</v>
       </c>
-      <c r="C63" s="36">
+      <c r="C63" s="37">
         <v>1.91</v>
       </c>
-      <c r="D63" s="36">
+      <c r="D63" s="37">
         <v>2.01</v>
       </c>
-      <c r="E63" s="36">
+      <c r="E63" s="37">
         <v>2.07</v>
       </c>
-      <c r="F63" s="36">
+      <c r="F63" s="37">
         <v>2.07</v>
       </c>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="34"/>
+      <c r="M63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>408</v>
-      </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
+      <c r="A64" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="32" t="s">
-        <v>409</v>
-      </c>
-      <c r="B65" s="36">
+      <c r="A65" s="33" t="s">
+        <v>411</v>
+      </c>
+      <c r="B65" s="37">
         <v>8.25</v>
       </c>
-      <c r="C65" s="36">
+      <c r="C65" s="37">
         <v>8.94</v>
       </c>
-      <c r="D65" s="36">
+      <c r="D65" s="37">
         <v>9.42</v>
       </c>
-      <c r="E65" s="36">
+      <c r="E65" s="37">
         <v>14.09</v>
       </c>
-      <c r="F65" s="36">
+      <c r="F65" s="37">
         <v>15.43</v>
       </c>
-      <c r="G65" s="36">
+      <c r="G65" s="37">
         <v>9.59</v>
       </c>
-      <c r="H65" s="36">
+      <c r="H65" s="37">
         <v>12.25</v>
       </c>
-      <c r="I65" s="36">
+      <c r="I65" s="37">
         <v>11.17</v>
       </c>
-      <c r="J65" s="36">
+      <c r="J65" s="37">
         <v>11.68</v>
       </c>
-      <c r="K65" s="33"/>
-      <c r="L65" s="33"/>
-      <c r="M65" s="33"/>
+      <c r="K65" s="34"/>
+      <c r="L65" s="34"/>
+      <c r="M65" s="34"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="32" t="s">
-        <v>410</v>
-      </c>
-      <c r="B66" s="36">
+      <c r="A66" s="33" t="s">
+        <v>412</v>
+      </c>
+      <c r="B66" s="37">
         <v>10.74</v>
       </c>
-      <c r="C66" s="36">
+      <c r="C66" s="37">
         <v>11.06</v>
       </c>
-      <c r="D66" s="36">
+      <c r="D66" s="37">
         <v>11.82</v>
       </c>
-      <c r="E66" s="36">
+      <c r="E66" s="37">
         <v>12.29</v>
       </c>
-      <c r="F66" s="36">
+      <c r="F66" s="37">
         <v>11.85</v>
       </c>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
-      <c r="J66" s="33"/>
-      <c r="K66" s="33"/>
-      <c r="L66" s="33"/>
-      <c r="M66" s="33"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="34"/>
+      <c r="K66" s="34"/>
+      <c r="L66" s="34"/>
+      <c r="M66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
+      <c r="A67" s="31" t="s">
+        <v>413</v>
+      </c>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="32" t="s">
-        <v>412</v>
-      </c>
-      <c r="B68" s="36">
+      <c r="A68" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="B68" s="37">
         <v>13.74</v>
       </c>
-      <c r="C68" s="36">
+      <c r="C68" s="37">
         <v>13.8</v>
       </c>
-      <c r="D68" s="36">
+      <c r="D68" s="37">
         <v>12.33</v>
       </c>
-      <c r="E68" s="36">
+      <c r="E68" s="37">
         <v>20.52</v>
       </c>
-      <c r="F68" s="36">
+      <c r="F68" s="37">
         <v>18.41</v>
       </c>
-      <c r="G68" s="36">
+      <c r="G68" s="37">
         <v>13.22</v>
       </c>
-      <c r="H68" s="36">
+      <c r="H68" s="37">
         <v>13.9</v>
       </c>
-      <c r="I68" s="36">
+      <c r="I68" s="37">
         <v>16.0</v>
       </c>
-      <c r="J68" s="36">
+      <c r="J68" s="37">
         <v>17.29</v>
       </c>
-      <c r="K68" s="33"/>
-      <c r="L68" s="33"/>
-      <c r="M68" s="33"/>
+      <c r="K68" s="34"/>
+      <c r="L68" s="34"/>
+      <c r="M68" s="34"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="32" t="s">
-        <v>413</v>
-      </c>
-      <c r="B69" s="36">
+      <c r="A69" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="B69" s="37">
         <v>15.38</v>
       </c>
-      <c r="C69" s="36">
+      <c r="C69" s="37">
         <v>15.21</v>
       </c>
-      <c r="D69" s="36">
+      <c r="D69" s="37">
         <v>15.2</v>
       </c>
-      <c r="E69" s="36">
+      <c r="E69" s="37">
         <v>16.04</v>
       </c>
-      <c r="F69" s="36">
+      <c r="F69" s="37">
         <v>15.5</v>
       </c>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
-      <c r="M69" s="33"/>
+      <c r="G69" s="34"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="34"/>
+      <c r="K69" s="34"/>
+      <c r="L69" s="34"/>
+      <c r="M69" s="34"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
+      <c r="A70" s="31" t="s">
+        <v>416</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="32" t="s">
-        <v>415</v>
-      </c>
-      <c r="B71" s="36">
+      <c r="A71" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="B71" s="37">
         <v>25.4</v>
       </c>
-      <c r="C71" s="36">
+      <c r="C71" s="37">
         <v>24.28</v>
       </c>
-      <c r="D71" s="36">
+      <c r="D71" s="37">
         <v>19.26</v>
       </c>
-      <c r="E71" s="36">
+      <c r="E71" s="37">
         <v>44.42</v>
       </c>
-      <c r="F71" s="36">
+      <c r="F71" s="37">
         <v>36.8</v>
       </c>
-      <c r="G71" s="36">
+      <c r="G71" s="37">
         <v>20.98</v>
       </c>
-      <c r="H71" s="36">
+      <c r="H71" s="37">
         <v>20.02</v>
       </c>
-      <c r="I71" s="36">
+      <c r="I71" s="37">
         <v>33.67</v>
       </c>
-      <c r="J71" s="36">
+      <c r="J71" s="37">
         <v>33.41</v>
       </c>
-      <c r="K71" s="33"/>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="34"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="32" t="s">
-        <v>416</v>
-      </c>
-      <c r="B72" s="36">
+      <c r="A72" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" s="37">
         <v>27.94</v>
       </c>
-      <c r="C72" s="36">
+      <c r="C72" s="37">
         <v>26.71</v>
       </c>
-      <c r="D72" s="36">
+      <c r="D72" s="37">
         <v>25.39</v>
       </c>
-      <c r="E72" s="36">
+      <c r="E72" s="37">
         <v>28.26</v>
       </c>
-      <c r="F72" s="36">
+      <c r="F72" s="37">
         <v>26.88</v>
       </c>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
-      <c r="M72" s="33"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="34"/>
+      <c r="K72" s="34"/>
+      <c r="L72" s="34"/>
+      <c r="M72" s="34"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
